--- a/out/Attention-mamba2_repeat_1_000008.xlsx
+++ b/out/Attention-mamba2_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.757166170459627</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC45" t="n">
-        <v>-5.991974801337346e-05</v>
+        <v>-8.908517028472852e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06883628181898091</v>
+        <v>-0.1023417502729988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.157166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.06894804136468831</v>
+        <v>-0.1025097581408063</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.1864041064805928</v>
+        <v>0.2837880463890378</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3042180743068245</v>
+        <v>0.4656112180782985</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01328125345009624</v>
+        <v>0.02021983872223807</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1440774620796377</v>
+        <v>0.2218076219583314</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02329079334800647</v>
+        <v>0.03545857947315587</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1773733630628721</v>
+        <v>0.272498451292105</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.02829525151042792</v>
+        <v>0.04307829822141423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2106714807530944</v>
+        <v>0.3231928376953367</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.007485855602677868</v>
+        <v>0.0113993390061749</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1973132978058534</v>
+        <v>0.3028586413121533</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004156802442709122</v>
+        <v>0.006331256169607655</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1981351378671369</v>
+        <v>0.3041124318635659</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.008737895483277709</v>
+        <v>0.01330510269712677</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2114598331057895</v>
+        <v>0.3243998215040392</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003429604798555914</v>
+        <v>0.005224415909789999</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.157166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2095739523046131</v>
+        <v>0.32153155804156</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002440958021675799</v>
+        <v>0.003719134956839246</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2110253469384802</v>
+        <v>0.3237432331153297</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.0009577448599815267</v>
+        <v>0.001460164603554397</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.210497607513502</v>
+        <v>0.3229428877413782</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005422016742883616</v>
+        <v>0.0008273631101851133</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2106223463206813</v>
+        <v>0.3231352369128624</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002028633538306648</v>
+        <v>0.0003120796922840649</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2104866090708552</v>
+        <v>0.3229313677799522</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>9.298547946403932e-05</v>
+        <v>0.0001436296598611833</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2104683936140628</v>
+        <v>0.322906321862346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.052231295157488e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2104371784607519</v>
+        <v>0.3228615570089519</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2104172789394388</v>
+        <v>0.3228340416141267</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.468432682490249e-07</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2104122707483762</v>
+        <v>0.3228290289552121</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2104077069978367</v>
+        <v>0.3228246473696513</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2104038064248979</v>
+        <v>0.3228212970148586</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.376196673809899e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2103985850129121</v>
+        <v>0.3228159276878708</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2103929230159083</v>
+        <v>0.3228099349544404</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2103927392734492</v>
+        <v>0.3228045671658621</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2103927760219409</v>
+        <v>0.3228046039143538</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2103928862674164</v>
+        <v>0.3228047141598293</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2103929597644</v>
+        <v>0.3228047876568129</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2103931435068592</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2103946869435157</v>
+        <v>0.3228065148359286</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.045076465039656</v>
+        <v>11.27907012395075</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2103961568831887</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.045076465039656</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2103974063319108</v>
+        <v>0.3228092342243237</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.645076465039656</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.210398766026108</v>
+        <v>0.322810593918521</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2103965611165988</v>
+        <v>0.3228083890090117</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2103961568831887</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2103958628952541</v>
+        <v>0.322807690787667</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2103955321588276</v>
+        <v>0.3228073600512406</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2103952381708932</v>
+        <v>0.3228070660633061</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2103948706859748</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2103947604404993</v>
+        <v>0.3228065883329122</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2103947236920076</v>
+        <v>0.3228065515844205</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2103948706859748</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2103943929555812</v>
+        <v>0.3228062208479941</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2103953484163685</v>
+        <v>0.3228071763087814</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2103949809314504</v>
+        <v>0.3228068088238633</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2103954219133523</v>
+        <v>0.3228072498057653</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2103947971889912</v>
+        <v>0.3228066250814041</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.210394613446532</v>
+        <v>0.3228064413389449</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.210394209213122</v>
+        <v>0.3228060371055349</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2103933639978101</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2103933272493184</v>
+        <v>0.3228051551417312</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2103934742432856</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.210393400746302</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2103934742432856</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2103935109917775</v>
+        <v>0.3228053388841904</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.210393400746302</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2103938417282039</v>
+        <v>0.3228056696206169</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2103937314827284</v>
+        <v>0.3228055593751413</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2103936947342365</v>
+        <v>0.3228055226266494</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2103936212372528</v>
+        <v>0.3228054491296657</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2103935844887611</v>
+        <v>0.3228054123811741</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2103933639978101</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2103932905008264</v>
+        <v>0.3228051183932393</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2103932170038428</v>
+        <v>0.3228050448962557</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.645076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2103932537523348</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.045076465039656</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2103931435068592</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2103932537523348</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.4785214654300936</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2103935477402692</v>
+        <v>0.3228053756326821</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000008.xlsx
+++ b/out/Attention-mamba2_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC45" t="n">
-        <v>-5.991974801337346e-05</v>
+        <v>-7.629606011637953e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06883628181898091</v>
+        <v>-0.08764951906461722</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.1986870573439082</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559279</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559279</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.157166170459627</v>
+        <v>0.4418255450559279</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559279</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559279</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439082</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0688962015669943</v>
+        <v>-0.08772581512473361</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439082</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.06894804136468831</v>
+        <v>-0.08780786795714358</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.1864041064805928</v>
+        <v>0.2950432985844145</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3042180743068245</v>
+        <v>0.5028452231490831</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01328125345009624</v>
+        <v>0.02102173649178622</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1440774620796377</v>
+        <v>0.2493721890476786</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02329079334800647</v>
+        <v>0.03686496325713078</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1773733630628721</v>
+        <v>0.3020735473709966</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.02829525151042792</v>
+        <v>0.04478688842633693</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2106714807530944</v>
+        <v>0.3547785965819354</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.007485855602677868</v>
+        <v>0.01185156780887777</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1973132978058534</v>
+        <v>0.3336379931565188</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004156802442709122</v>
+        <v>0.006582563880578718</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.045076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1981351378671369</v>
+        <v>0.3349417096837126</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.008737895483277709</v>
+        <v>0.01383380741341101</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2114598331057895</v>
+        <v>0.3560339322080279</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003429604798555914</v>
+        <v>0.005431509499547778</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.157166170459627</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2095739523046131</v>
+        <v>0.3530522787381185</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002440958021675799</v>
+        <v>0.003865754443328981</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2110253469384802</v>
+        <v>0.3553517389629691</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.0009577448599815267</v>
+        <v>0.001518553925104757</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.045076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.210497607513502</v>
+        <v>0.3545197123571099</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005422016742883616</v>
+        <v>0.0008597327866923123</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2106223463206813</v>
+        <v>0.3547199199610555</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002028633538306648</v>
+        <v>0.0003249977538215638</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2104866090708552</v>
+        <v>0.35450794875236</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>9.298547946403932e-05</v>
+        <v>0.0001491344620782641</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2104683936140628</v>
+        <v>0.3544820868963772</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.052231295157488e-05</v>
+        <v>5.151277060477821e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2104371784607519</v>
+        <v>0.3544355546907983</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2104172789394388</v>
+        <v>0.3544070463420521</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.468432682490249e-07</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2104122707483762</v>
+        <v>0.3544020329384955</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2104077069978367</v>
+        <v>0.3543976873126861</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.045076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2104038064248979</v>
+        <v>0.3543943369578934</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.376196673809899e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2103985850129121</v>
+        <v>0.3543889676309055</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2103929230159083</v>
+        <v>0.3543829748974752</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2103927392734492</v>
+        <v>0.3543776071088968</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2103927760219409</v>
+        <v>0.3543776438573885</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2103928862674164</v>
+        <v>0.3543777541028641</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2103929597644</v>
+        <v>0.3543778275998477</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.645076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2103931435068592</v>
+        <v>0.3543780113423068</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2103946869435157</v>
+        <v>0.3543795547789633</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2103961568831887</v>
+        <v>0.3543810247186364</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2103974063319108</v>
+        <v>0.3543822741673584</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.210398766026108</v>
+        <v>0.3543836338615557</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439081</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2103965611165988</v>
+        <v>0.3543814289520464</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2103961568831887</v>
+        <v>0.3543810247186364</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439082</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3543801795033245</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2103958628952541</v>
+        <v>0.3543807307307017</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2103955321588276</v>
+        <v>0.3543803999942753</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2103952381708932</v>
+        <v>0.3543801060063408</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3543801795033245</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2103948706859748</v>
+        <v>0.3543797385214225</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2103947604404993</v>
+        <v>0.3543796282759469</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2103947236920076</v>
+        <v>0.3543795915274552</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2103948706859748</v>
+        <v>0.3543797385214225</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2103943929555812</v>
+        <v>0.3543792607910288</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.045076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2103953484163685</v>
+        <v>0.3543802162518161</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2103953116678768</v>
+        <v>0.3543801795033245</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2103949809314504</v>
+        <v>0.354379848766898</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2103954219133523</v>
+        <v>0.3543802897488</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2103947971889912</v>
+        <v>0.3543796650244389</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.210394613446532</v>
+        <v>0.3543794812819797</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.210394209213122</v>
+        <v>0.3543790770485697</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2103933639978101</v>
+        <v>0.3543782318332577</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2103933272493184</v>
+        <v>0.354378195084766</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.645076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2103934742432856</v>
+        <v>0.3543783420787333</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.210393400746302</v>
+        <v>0.3543782685817496</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2103934742432856</v>
+        <v>0.3543783420787333</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.645076465039656</v>
+        <v>0.4418255450559281</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2103935109917775</v>
+        <v>0.3543783788272252</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.757166170459627</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.210393400746302</v>
+        <v>0.3543782685817496</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2103938417282039</v>
+        <v>0.3543787095636516</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.045076465039656</v>
+        <v>0.8823381474557639</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2103937314827284</v>
+        <v>0.3543785993181761</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2103936947342365</v>
+        <v>0.3543785625696841</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2103936212372528</v>
+        <v>0.3543784890727005</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2103935844887611</v>
+        <v>0.3543784523242088</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2103933639978101</v>
+        <v>0.3543782318332577</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2103932905008264</v>
+        <v>0.3543781583362741</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2103932170038428</v>
+        <v>0.3543780848392905</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.645076465039656</v>
+        <v>1.082338147455764</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2103932537523348</v>
+        <v>0.3543781215877824</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.045076465039656</v>
+        <v>0.241825545055928</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2103931435068592</v>
+        <v>0.3543780113423068</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.757166170459627</v>
+        <v>-0.3986870573439081</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2103932537523348</v>
+        <v>0.3543781215877824</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.757166170459627</v>
+        <v>-1.039199659743745</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2103935477402692</v>
+        <v>0.3543784155757169</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000008.xlsx
+++ b/out/Attention-mamba2_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2586995363235474</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3731203377246857</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.6024197936058044</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.4323036968708038</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.4703856110572815</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1803253144025803</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1041929870843887</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2112302482128143</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2155406773090363</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.1981074959039688</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1989478766918182</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.1951410621404648</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1788034290075302</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.1728270798921585</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.3165826201438904</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.238137885928154</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.3</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.1556581109762192</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1536182910203934</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.1533486843109131</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1368533819913864</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.134640172123909</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.1326400339603424</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.1328763365745544</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1510616987943649</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.1526763886213303</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.1336069703102112</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.1332700699567795</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1292463690042496</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.1360730677843094</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.1595965474843979</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2072966992855072</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2649696171283722</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.1969689577817917</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.1802826225757599</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1706875860691071</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.1814655214548111</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.149245098233223</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1346821635961533</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.2211555391550064</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.2751403748989105</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.2528016865253448</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.4092980921268463</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.4971795380115509</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.08974370360374451</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.629606011637953e-05</v>
+        <v>-0.0001100360487170983</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08764951906461722</v>
+        <v>-0.12641028560471</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1265411078929901</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.039199659743745</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.1710636913776398</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1986870573439082</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.07427132129669189</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4418255450559279</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.03433408960700035</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.09491978585720062</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.4418255450559279</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.2119151204824448</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.4418255450559279</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.09447206556797028</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4418255450559279</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.04986914247274399</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.082338147455764</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.09770499169826508</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.082338147455764</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.06947247684001923</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.082338147455764</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.1219959408044815</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.082338147455764</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.1073092818260193</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4418255450559279</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.02660888992249966</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3986870573439082</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.08772581512473361</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.09138931334018707</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3986870573439082</v>
+        <v>-0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.08780786795714358</v>
+        <v>-0.1266041442637311</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2950432985844145</v>
+        <v>0.3014070168405988</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03949551284313202</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5028452231490831</v>
+        <v>0.4767886019269475</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02102173649178622</v>
+        <v>0.02147518666770462</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.02032237499952316</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2493721890476786</v>
+        <v>0.2178484684838639</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03686496325713078</v>
+        <v>0.03766003204595456</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.008158944547176361</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4418255450559281</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3020735473709966</v>
+        <v>0.2716864360790085</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04478688842633693</v>
+        <v>0.04575280310787899</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007665261626243591</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4418255450559281</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3547785965819354</v>
+        <v>0.3255281702129909</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01185156780887777</v>
+        <v>0.01210733804785414</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.07330719381570816</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.241825545055928</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3336379931565188</v>
+        <v>0.303931628985415</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006582563880578718</v>
+        <v>0.006724543565463101</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.02070135623216629</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3349417096837126</v>
+        <v>0.3052635518668094</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01383380741341101</v>
+        <v>0.01413130015464384</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.02167261764407158</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4418255450559281</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3560339322080279</v>
+        <v>0.3268104771803759</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005431509499547778</v>
+        <v>0.005548983641106284</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01920265331864357</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4418255450559281</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3530522787381185</v>
+        <v>0.323764503062977</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003865754443328981</v>
+        <v>0.003950276264952474</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0386967733502388</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.241825545055928</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3553517389629691</v>
+        <v>0.3261137577846784</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001518553925104757</v>
+        <v>0.001551143313877052</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0178929939866066</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3545197123571099</v>
+        <v>0.3252640486307777</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008597327866923123</v>
+        <v>0.0008782297446964257</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.04391637444496155</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.082338147455764</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3547199199610555</v>
+        <v>0.3254686417718674</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003249977538215638</v>
+        <v>0.0003320439692056542</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04529282450675964</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.082338147455764</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.35450794875236</v>
+        <v>0.3252522512491071</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001491344620782641</v>
+        <v>0.0001524373434085126</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.0530695915222168</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3544820868963772</v>
+        <v>0.3252259439282887</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.151277060477821e-05</v>
+        <v>5.312742119348616e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.04504193365573883</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3544355546907983</v>
+        <v>0.3251785274758544</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.04916970431804657</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3544070463420521</v>
+        <v>0.3251496876460397</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.06033029407262802</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3544020329384955</v>
+        <v>0.3251446742424832</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.05639518797397614</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3543976873126861</v>
+        <v>0.3251403286166738</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.07915414869785309</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3543943369578934</v>
+        <v>0.325136978261881</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.06140665709972382</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3543889676309055</v>
+        <v>0.3251316089348933</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.05865810811519623</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3543829748974752</v>
+        <v>0.3251256162014629</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.05914966017007828</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.16</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3543776071088968</v>
+        <v>0.3251202484128846</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.03047045320272446</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3543776438573885</v>
+        <v>0.3251202851613763</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.06375805288553238</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3543777541028641</v>
+        <v>0.3251203954068518</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.08591466397047043</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3543778275998477</v>
+        <v>0.3251204689038354</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.05731735378503799</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3543780113423068</v>
+        <v>0.3251206526462946</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.03046885132789612</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3543795547789633</v>
+        <v>0.325122196082951</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.08144509792327881</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3543810247186364</v>
+        <v>0.3251236660226241</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.06624886393547058</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3543822741673584</v>
+        <v>0.3251249154713461</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.00687364861369133</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4418255450559281</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3543836338615557</v>
+        <v>0.3251262751655434</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.06535939872264862</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3986870573439081</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3543814289520464</v>
+        <v>0.3251240702560341</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01254420727491379</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.039199659743745</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3543810247186364</v>
+        <v>0.3251236660226241</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.05002469569444656</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3986870573439082</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3543801795033245</v>
+        <v>0.3251228208073121</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.0169035941362381</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3543807307307017</v>
+        <v>0.3251233720346894</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.03250985592603683</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.082338147455764</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3543803999942753</v>
+        <v>0.325123041298263</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02673694491386414</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.082338147455764</v>
+        <v>0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3543801060063408</v>
+        <v>0.3251227473103285</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.02488766610622406</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3543801795033245</v>
+        <v>0.3251228208073121</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.04106492549180984</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3543797385214225</v>
+        <v>0.3251223798254102</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03925846517086029</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3543796282759469</v>
+        <v>0.3251222695799347</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.03839033842086792</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.082338147455764</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3543795915274552</v>
+        <v>0.325122232831443</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.03621207177639008</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.082338147455764</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3543797385214225</v>
+        <v>0.3251223798254102</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01764042675495148</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.082338147455764</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3543792607910288</v>
+        <v>0.3251219020950166</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02044164761900902</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.082338147455764</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3543802162518161</v>
+        <v>0.3251228575558038</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01499772071838379</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3543801795033245</v>
+        <v>0.3251228208073121</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.03434541076421738</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.354379848766898</v>
+        <v>0.3251224900708857</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.0389883890748024</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8823381474557639</v>
+        <v>-0.3</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3543802897488</v>
+        <v>0.3251229310527877</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.03223849833011627</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3543796650244389</v>
+        <v>0.3251223063284266</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.03229283541440964</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.241825545055928</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3543794812819797</v>
+        <v>0.3251221225859674</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001122236135415733</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.241825545055928</v>
+        <v>0.16</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3543790770485697</v>
+        <v>0.3251217183525574</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.005072258412837982</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.241825545055928</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3543782318332577</v>
+        <v>0.3251208731372454</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.04557673633098602</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.3</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.354378195084766</v>
+        <v>0.3251208363887537</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02163314819335938</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3543783420787333</v>
+        <v>0.3251209833827209</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.05527883023023605</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3543782685817496</v>
+        <v>0.3251209098857373</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01894618943333626</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.082338147455764</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3543783420787333</v>
+        <v>0.3251209833827209</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.05138522386550903</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.4418255450559281</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3543783788272252</v>
+        <v>0.3251210201312129</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.02434440702199936</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.241825545055928</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3543782685817496</v>
+        <v>0.3251209098857373</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.06191447377204895</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.241825545055928</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3543787095636516</v>
+        <v>0.3251213508676393</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.05096400529146194</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.8823381474557639</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3543785993181761</v>
+        <v>0.3251212406221637</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.0761977955698967</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3543785625696841</v>
+        <v>0.3251212038736718</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.05133994668722153</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.082338147455764</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3543784890727005</v>
+        <v>0.3251211303766882</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.05500471591949463</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.082338147455764</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3543784523242088</v>
+        <v>0.3251210936281965</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.07433352619409561</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.082338147455764</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3543782318332577</v>
+        <v>0.3251208731372454</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.05582201480865479</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.082338147455764</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3543781583362741</v>
+        <v>0.3251207996402618</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.07628260552883148</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.082338147455764</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3543780848392905</v>
+        <v>0.3251207261432782</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.06796272099018097</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.082338147455764</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3543781215877824</v>
+        <v>0.3251207628917701</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.05413921922445297</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.241825545055928</v>
+        <v>-0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3543780113423068</v>
+        <v>0.3251206526462946</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.02930676192045212</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3986870573439081</v>
+        <v>-0.7200000000000006</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3543781215877824</v>
+        <v>0.3251207628917701</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.03079487383365631</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.039199659743745</v>
+        <v>-1.140000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3543784155757169</v>
+        <v>0.3251210568797046</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000008.xlsx
+++ b/out/Attention-mamba2_repeat_1_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.2586995363235474</v>
+        <v>-0.258706271648407</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3731203377246857</v>
+        <v>-0.3731260895729065</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.6024197936058044</v>
+        <v>-0.6024226546287537</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.4323036968708038</v>
+        <v>-0.4323027729988098</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.4703856110572815</v>
+        <v>-0.4703856408596039</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1803253144025803</v>
+        <v>-0.1803262084722519</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1041929870843887</v>
+        <v>-0.1041940078139305</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2112302482128143</v>
+        <v>-0.2112350016832352</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2155406773090363</v>
+        <v>-0.215545579791069</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.1981074959039688</v>
+        <v>-0.1981120258569717</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1989478766918182</v>
+        <v>-0.1989524513483047</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.1951410621404648</v>
+        <v>-0.1951458156108856</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1788034290075302</v>
+        <v>-0.1788083165884018</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.1728270798921585</v>
+        <v>-0.1728318184614182</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.2599999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.3165826201438904</v>
+        <v>-0.3165877759456635</v>
       </c>
       <c r="JB16" t="n">
         <v>0.02000000000000007</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.238137885928154</v>
+        <v>-0.2381429374217987</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.1556581109762192</v>
+        <v>-0.1556629687547684</v>
       </c>
       <c r="JB18" t="n">
         <v>0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1536182910203934</v>
+        <v>-0.1536230146884918</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.1533486843109131</v>
+        <v>-0.1533534079790115</v>
       </c>
       <c r="JB20" t="n">
         <v>0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1368533819913864</v>
+        <v>-0.1368581503629684</v>
       </c>
       <c r="JB21" t="n">
         <v>0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.134640172123909</v>
+        <v>-0.1346449255943298</v>
       </c>
       <c r="JB22" t="n">
         <v>0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.1326400339603424</v>
+        <v>-0.1326448768377304</v>
       </c>
       <c r="JB23" t="n">
         <v>0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.1328763365745544</v>
+        <v>-0.1328810304403305</v>
       </c>
       <c r="JB24" t="n">
         <v>0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1510616987943649</v>
+        <v>-0.151066467165947</v>
       </c>
       <c r="JB25" t="n">
         <v>0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.1526763886213303</v>
+        <v>-0.1526811569929123</v>
       </c>
       <c r="JB26" t="n">
         <v>0.1199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.1336069703102112</v>
+        <v>-0.1336116790771484</v>
       </c>
       <c r="JB27" t="n">
         <v>0.1199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.1332700699567795</v>
+        <v>-0.1332746595144272</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1292463690042496</v>
+        <v>-0.1292509734630585</v>
       </c>
       <c r="JB29" t="n">
         <v>0.1199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.1360730677843094</v>
+        <v>-0.1360777467489243</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.02000000000000007</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.1595965474843979</v>
+        <v>-0.1596011072397232</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2072966992855072</v>
+        <v>-0.2072969377040863</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2649696171283722</v>
+        <v>-0.2649743854999542</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.1969689577817917</v>
+        <v>-0.1969736069440842</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.1802826225757599</v>
+        <v>-0.18028724193573</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.1706875860691071</v>
+        <v>-0.1706922352313995</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.1814655214548111</v>
+        <v>-0.1814702153205872</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.1600000000000001</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.149245098233223</v>
+        <v>-0.1492497771978378</v>
       </c>
       <c r="JB38" t="n">
         <v>0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1346821635961533</v>
+        <v>-0.1346867382526398</v>
       </c>
       <c r="JB39" t="n">
         <v>0.1600000000000001</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.2211555391550064</v>
+        <v>-0.221160352230072</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.2751403748989105</v>
+        <v>-0.2751452624797821</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.2528016865253448</v>
+        <v>-0.2528064846992493</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.4092980921268463</v>
+        <v>-0.4092988967895508</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.4971795380115509</v>
+        <v>-0.4971790015697479</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.08974370360374451</v>
+        <v>-0.08974047005176544</v>
       </c>
       <c r="JB45" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1265411078929901</v>
+        <v>-0.126537099480629</v>
       </c>
       <c r="JB46" t="n">
         <v>0.7199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.1710636913776398</v>
+        <v>-0.1710604280233383</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.07427132129669189</v>
+        <v>0.07427386194467545</v>
       </c>
       <c r="JB48" t="n">
         <v>0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.03433408960700035</v>
+        <v>0.03433548286557198</v>
       </c>
       <c r="JB49" t="n">
         <v>0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.09491978585720062</v>
+        <v>0.09492034465074539</v>
       </c>
       <c r="JB50" t="n">
         <v>0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.2119151204824448</v>
+        <v>-0.2119209617376328</v>
       </c>
       <c r="JB51" t="n">
         <v>0.5799999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.09447206556797028</v>
+        <v>0.09447164833545685</v>
       </c>
       <c r="JB52" t="n">
         <v>0.5799999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.04986914247274399</v>
+        <v>0.04986947774887085</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.16</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.09770499169826508</v>
+        <v>0.09770528972148895</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.06947247684001923</v>
+        <v>0.06947331130504608</v>
       </c>
       <c r="JB55" t="n">
         <v>0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.1219959408044815</v>
+        <v>0.1219966039061546</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1073092818260193</v>
+        <v>0.1073104366660118</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.02000000000000007</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.02660888992249966</v>
+        <v>-0.02660530619323254</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.09138931334018707</v>
+        <v>-0.09138669073581696</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.03949551284313202</v>
+        <v>0.03949578851461411</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.3</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.02032237499952316</v>
+        <v>0.0203230008482933</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.008158944547176361</v>
+        <v>0.008159540593624115</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.007665261626243591</v>
+        <v>-0.007664330769330263</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.02000000000000007</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.07330719381570816</v>
+        <v>0.07330498844385147</v>
       </c>
       <c r="JB64" t="n">
         <v>0.7199999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.02070135623216629</v>
+        <v>0.02070195972919464</v>
       </c>
       <c r="JB65" t="n">
         <v>0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.02167261764407158</v>
+        <v>0.02166440710425377</v>
       </c>
       <c r="JB66" t="n">
         <v>0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.01920265331864357</v>
+        <v>-0.01921870931982994</v>
       </c>
       <c r="JB67" t="n">
         <v>0.5799999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.0178929939866066</v>
+        <v>0.01789124310016632</v>
       </c>
       <c r="JB69" t="n">
         <v>0.7199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.04391637444496155</v>
+        <v>0.04391604661941528</v>
       </c>
       <c r="JB70" t="n">
         <v>0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.04529282450675964</v>
+        <v>0.0452922061085701</v>
       </c>
       <c r="JB71" t="n">
         <v>0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.0530695915222168</v>
+        <v>0.05306851118803024</v>
       </c>
       <c r="JB72" t="n">
         <v>0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.04504193365573883</v>
+        <v>0.04504149407148361</v>
       </c>
       <c r="JB73" t="n">
         <v>0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.04916970431804657</v>
+        <v>0.04916898906230927</v>
       </c>
       <c r="JB74" t="n">
         <v>0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.06033029407262802</v>
+        <v>0.06032920628786087</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.05639518797397614</v>
+        <v>0.05639436095952988</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.07915414869785309</v>
+        <v>0.07915122807025909</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.06140665709972382</v>
+        <v>0.06140541285276413</v>
       </c>
       <c r="JB78" t="n">
         <v>0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.05865810811519623</v>
+        <v>0.05865693837404251</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.02000000000000007</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.05914966017007828</v>
+        <v>0.05914859473705292</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.16</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.03047045320272446</v>
+        <v>-0.03047002106904984</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.1600000000000001</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.06375805288553238</v>
+        <v>0.06375671923160553</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.08591466397047043</v>
+        <v>0.0859011709690094</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.05731735378503799</v>
+        <v>0.05731669068336487</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.16</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.03046885132789612</v>
+        <v>-0.03047214448451996</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.08144509792327881</v>
+        <v>0.0814388245344162</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.06624886393547058</v>
+        <v>0.06624659895896912</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.00687364861369133</v>
+        <v>0.006874568294733763</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.06535939872264862</v>
+        <v>-0.06535738706588745</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.7199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.01254420727491379</v>
+        <v>-0.0125836506485939</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.05002469569444656</v>
+        <v>-0.05002401769161224</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.0169035941362381</v>
+        <v>0.016903355717659</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.7199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.03250985592603683</v>
+        <v>0.03250937163829803</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02673694491386414</v>
+        <v>0.02673683315515518</v>
       </c>
       <c r="JB94" t="n">
         <v>0.3</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.02488766610622406</v>
+        <v>0.0248875617980957</v>
       </c>
       <c r="JB95" t="n">
         <v>0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.04106492549180984</v>
+        <v>0.04106415808200836</v>
       </c>
       <c r="JB96" t="n">
         <v>0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.03925846517086029</v>
+        <v>0.03925768285989761</v>
       </c>
       <c r="JB97" t="n">
         <v>0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.03839033842086792</v>
+        <v>0.03838958591222763</v>
       </c>
       <c r="JB98" t="n">
         <v>0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.03621207177639008</v>
+        <v>0.03621185570955276</v>
       </c>
       <c r="JB99" t="n">
         <v>0.02000000000000007</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01764042675495148</v>
+        <v>0.01762363314628601</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.02044164761900902</v>
+        <v>0.0204375796020031</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.01499772071838379</v>
+        <v>0.01499775052070618</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.03434541076421738</v>
+        <v>0.03434530645608902</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.0389883890748024</v>
+        <v>0.03898788243532181</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.03223849833011627</v>
+        <v>0.03223831206560135</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.03229283541440964</v>
+        <v>0.03229264914989471</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001122236135415733</v>
+        <v>-0.00114309077616781</v>
       </c>
       <c r="JB107" t="n">
         <v>0.16</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.005072258412837982</v>
+        <v>0.005050561856478453</v>
       </c>
       <c r="JB108" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.04557673633098602</v>
+        <v>0.04557634145021439</v>
       </c>
       <c r="JB109" t="n">
         <v>0.3</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.02163314819335938</v>
+        <v>0.02163062244653702</v>
       </c>
       <c r="JB110" t="n">
         <v>0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.05527883023023605</v>
+        <v>0.05527845770120621</v>
       </c>
       <c r="JB111" t="n">
         <v>0.7199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.01894618943333626</v>
+        <v>0.01894430071115494</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.05138522386550903</v>
+        <v>0.05138470232486725</v>
       </c>
       <c r="JB113" t="n">
         <v>0.5799999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.02434440702199936</v>
+        <v>-0.02434377372264862</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.06191447377204895</v>
+        <v>0.06191376596689224</v>
       </c>
       <c r="JB115" t="n">
         <v>0.5799999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.05096400529146194</v>
+        <v>0.0509631484746933</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.0761977955698967</v>
+        <v>0.07616236060857773</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.05133994668722153</v>
+        <v>0.05133858323097229</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.05500471591949463</v>
+        <v>0.05500034242868423</v>
       </c>
       <c r="JB119" t="n">
         <v>0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.07433352619409561</v>
+        <v>0.07433096319437027</v>
       </c>
       <c r="JB120" t="n">
         <v>0.8599999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.05582201480865479</v>
+        <v>0.0558207631111145</v>
       </c>
       <c r="JB121" t="n">
         <v>0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.07628260552883148</v>
+        <v>0.07623748481273651</v>
       </c>
       <c r="JB122" t="n">
         <v>0.8599999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.06796272099018097</v>
+        <v>0.06790754199028015</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.05413921922445297</v>
+        <v>0.05413839966058731</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.3</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.02930676192045212</v>
+        <v>-0.02930612117052078</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.7200000000000006</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.03079487383365631</v>
+        <v>-0.03079444915056229</v>
       </c>
       <c r="JB126" t="n">
         <v>-1.140000000000001</v>
